--- a/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo entre dans la cuisine. Maman coupe des pommes. Ça sent le sucré. Hugo a soif. Sa bouche est sèche. Sa langue colle. Hugo dit : j'ai soif, maman. Maman sourit. Maman prend un verre. Le verre est bleu. Elle verse de l'eau. L'eau est claire. Hugo prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Maman dit : quand on a soif, on boit de l'eau. Dans un verre. Hugo pose le verre. Il se sent mieux.</t>
+          <t>Hugo entre dans la cuisine. Maman coupe des pommes. Ça sent le sucré. Hugo a soif. Sa bouche est sèche. Sa langue colle. J'ai soif, maman. Maman sourit. Maman prend un verre. Le verre est bleu. Elle verse de l'eau. L'eau est claire. Hugo prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Hugo pose le verre. Il se sent mieux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo entre dans la cuisine. Maman coupe des pommes. Ça sent le sucré. Hugo a soif. Sa bouche est sèche. Sa langue colle.
+enfant-m|J'ai soif, maman. Maman sourit. Maman prend un verre.
+narrateur|Le verre est bleu. Elle verse de l'eau. L'eau est claire. Hugo prend le verre. Il boit une gorgée. C'est frais. Il boit encore.
+maman|Quand on a soif, on boit de l'eau.
+narrateur|Dans un verre. Hugo pose le verre. Il se sent mieux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a soif. Que prend-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo avait soif. Il a pris le verre. Il a bu de l'eau. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo croque un morceau de pomme. Le verre reste sur la table. Merci, dit Hugo.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Dans un verre. Hugo pose le verre. Il se sent mieux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Hugo a soif. Que prend-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Hugo avait soif. Il a pris le verre. Il a bu de l'eau. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Hugo croque un morceau de pomme. Le verre reste sur la table. Merci, dit Hugo.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le verre d'eau de Hugo</t>
+          <t>Le verre bleu de Nino</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les pelures de pomme s'enroulent. Une abeille tapote la vitre. Nino a soif. Maman verse de l'eau dans un verre bleu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo entre dans la cuisine. Maman coupe des pommes. Ça sent le sucré. Hugo a soif. Sa bouche est sèche. Sa langue colle. J'ai soif, maman. Maman sourit. Maman prend un verre. Le verre est bleu. Elle verse de l'eau. L'eau est claire. Hugo prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Hugo pose le verre. Il se sent mieux.</t>
+          <t>Les pelures de pomme s'enroulent. Elles font des rubans jaunes. Elles reposent sur la planche. Ça sent le sucré. Une abeille tapote la vitre. Tic. Tic. Nino habite ici, avec maman. Papa est au jardin, tout près. Le soleil entre sur la table. Tu as vu les rubans, Nino ? Ce sont des pelures, maman. Oui. Des rubans de pomme. On les pose dans le bol ? Oui, maman. Nino aide un peu. La planche est lisse. En ce moment, Nino a soif. Sa bouche est sèche. Sa langue colle. J'ai soif, maman. On prend un verre ? Oui. Maman prend un verre. Le verre est bleu. Elle verse de l'eau. L'eau est claire. Tu prends le verre d'eau ? Nino prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Nino pose le verre. Tu te sens mieux ? Oui, maman. Bravo, Nino. Tu as bu de l'eau. L'abeille tapote encore un peu. Tu l'entends, l'abeille ? Oui. Tic. Tic. Une goutte reste sur le verre bleu. Tu as vu la goutte ? Elle glisse, maman. Oui. Tout doux. Tu restes près de la table ? Oui. Ça sent encore la pomme. Nino tient le verre à deux mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo entre dans la cuisine. Maman coupe des pommes. Ça sent le sucré. Hugo a soif. Sa bouche est sèche. Sa langue colle.
-enfant-m|J'ai soif, maman. Maman sourit. Maman prend un verre.
-narrateur|Le verre est bleu. Elle verse de l'eau. L'eau est claire. Hugo prend le verre. Il boit une gorgée. C'est frais. Il boit encore.
+          <t>narrateur|Les pelures de pomme s'enroulent.
+narrateur|Elles font des rubans jaunes.
+narrateur|Elles reposent sur la planche.
+narrateur|Ça sent le sucré.
+narrateur|Une abeille tapote la vitre.
+narrateur|Tic. Tic.
+narrateur|Nino habite ici, avec maman.
+narrateur|Papa est au jardin, tout près.
+narrateur|Le soleil entre sur la table.
+maman|Tu as vu les rubans, Nino ?
+enfant-m|Ce sont des pelures, maman.
+maman|Oui.
+maman|Des rubans de pomme.
+maman|On les pose dans le bol ?
+enfant-m|Oui, maman.
+narrateur|Nino aide un peu.
+narrateur|La planche est lisse.
+narrateur|En ce moment, Nino a soif.
+narrateur|Sa bouche est sèche.
+narrateur|Sa langue colle.
+enfant-m|J'ai soif, maman.
+maman|On prend un verre ?
+enfant-m|Oui.
+narrateur|Maman prend un verre.
+narrateur|Le verre est bleu.
+narrateur|Elle verse de l'eau.
+narrateur|L'eau est claire.
+maman|Tu prends le verre d'eau ?
+narrateur|Nino prend le verre.
+narrateur|Il boit une gorgée.
+narrateur|C'est frais.
+narrateur|Il boit encore.
 maman|Quand on a soif, on boit de l'eau.
-narrateur|Dans un verre. Hugo pose le verre. Il se sent mieux.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Dans un verre.
+narrateur|Nino pose le verre.
+maman|Tu te sens mieux ?
+enfant-m|Oui, maman.
+maman|Bravo, Nino.
+maman|Tu as bu de l'eau.
+narrateur|L'abeille tapote encore un peu.
+maman|Tu l'entends, l'abeille ?
+enfant-m|Oui.
+enfant-m|Tic. Tic.
+narrateur|Une goutte reste sur le verre bleu.
+maman|Tu as vu la goutte ?
+enfant-m|Elle glisse, maman.
+maman|Oui. Tout doux.
+maman|Tu restes près de la table ?
+enfant-m|Oui.
+narrateur|Ça sent encore la pomme.
+narrateur|Nino tient le verre à deux mains.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>verre,eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo a soif. Que prend-il ?</t>
+          <t>Nino a soif. Que prend-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a soif. Que prend-il ?</t>
+          <t>narrateur|Nino a soif.
+narrateur|Que prend-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo avait soif. Il a pris le verre. Il a bu de l'eau. Maman était là.</t>
+          <t>Nino avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. C'est du bon travail. Le verre est bleu, maman. Oui. Il est tout bleu. Tu veux encore une gorgée ? Oui. Nino boit encore un peu. Il pose le verre. Le verre reste sur la table ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1744,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo avait soif. Il a pris le verre. Il a bu de l'eau. Maman était là.</t>
+          <t>narrateur|Nino avait soif.
+narrateur|Il a pris le verre.
+narrateur|Il a bu de l'eau.
+maman|Bravo.
+maman|C'est du bon travail.
+enfant-m|Le verre est bleu, maman.
+maman|Oui. Il est tout bleu.
+maman|Tu veux encore une gorgée ?
+enfant-m|Oui.
+narrateur|Nino boit encore un peu.
+narrateur|Il pose le verre.
+maman|Le verre reste sur la table ?
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo croque un morceau de pomme. Le verre reste sur la table. Merci, dit Hugo.</t>
+          <t>Tu veux un morceau de pomme ? Oui, maman. Nino croque un morceau. Ça croque. C'est sucré. Oui. Sucré et croquant. Tu as fini de poser le verre ? Oui. Bravo. Le verre bleu reste sur la table. Les rubans jaunes restent dans le bol. L'abeille s'en va, hein ? Oui. Elle est partie. Merci, maman. Merci, Nino. On reste un moment à table ? Oui. Nino reste près de maman. Tu as fini ta petite pomme ? Oui, maman. Bravo. La planche est propre, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1924,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo croque un morceau de pomme. Le verre reste sur la table. Merci, dit Hugo.</t>
+          <t>maman|Tu veux un morceau de pomme ?
+enfant-m|Oui, maman.
+narrateur|Nino croque un morceau.
+narrateur|Ça croque.
+enfant-m|C'est sucré.
+maman|Oui. Sucré et croquant.
+maman|Tu as fini de poser le verre ?
+enfant-m|Oui.
+maman|Bravo.
+narrateur|Le verre bleu reste sur la table.
+narrateur|Les rubans jaunes restent dans le bol.
+maman|L'abeille s'en va, hein ?
+enfant-m|Oui. Elle est partie.
+enfant-m|Merci, maman.
+maman|Merci, Nino.
+maman|On reste un moment à table ?
+enfant-m|Oui.
+narrateur|Nino reste près de maman.
+maman|Tu as fini ta petite pomme ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|La planche est propre, maintenant.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1973,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nino. Tu as fait du bon travail. Le verre bleu brille encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2113,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'avais soif.
+enfant-m|J'ai bu de l'eau.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+narrateur|Le verre bleu brille encore un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2178,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les pelures de pomme s'enroulent. Elles font des rubans jaunes. Elles reposent sur la planche. Ça sent le sucré. Une abeille tapote la vitre. Tic. Tic. Nino habite ici, avec maman. Papa est au jardin, tout près. Le soleil entre sur la table. Tu as vu les rubans, Nino ? Ce sont des pelures, maman. Oui. Des rubans de pomme. On les pose dans le bol ? Oui, maman. Nino aide un peu. La planche est lisse. En ce moment, Nino a soif. Sa bouche est sèche. Sa langue colle. J'ai soif, maman. On prend un verre ? Oui. Maman prend un verre. Le verre est bleu. Elle verse de l'eau. L'eau est claire. Tu prends le verre d'eau ? Nino prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Nino pose le verre. Tu te sens mieux ? Oui, maman. Bravo, Nino. Tu as bu de l'eau. L'abeille tapote encore un peu. Tu l'entends, l'abeille ? Oui. Tic. Tic. Une goutte reste sur le verre bleu. Tu as vu la goutte ? Elle glisse, maman. Oui. Tout doux. Tu restes près de la table ? Oui. Ça sent encore la pomme. Nino tient le verre à deux mains.</t>
+          <t>Les pelures de pomme s'enroulent. Elles font des rubans jaunes. Elles reposent sur la planche. Ça sent le sucré. Une abeille tapote la vitre. Tic. Tic. Nino habite ici, avec maman. Papa est au jardin, tout près. Le soleil entre sur la table. Tu as vu les rubans, Nino ? Ce sont des pelures, maman. Oui. Des rubans de pomme. On les pose dans le bol ? Oui, maman. Nino aide un peu. La planche est lisse. En ce moment, Nino a soif. Sa bouche est sèche. Sa langue colle. J'ai soif, maman. On prend un verre ? Oui. Maman prend un verre. Le verre est bleu. Elle verse de l'eau. L'eau est claire. Tu prends le verre d'eau ? Nino prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Nino pose le verre. Tu te sens mieux ? Oui, maman. Bravo, Nino. Tu as bu de l'eau. L'abeille tapote encore un peu. Tu l'entends, l'abeille ? Oui. Tic. Tic. Une goutte reste sur le verre bleu. Tu as vu la goutte ? Elle glisse, maman. Oui. Tout doux. Tu restes près de la table ? Oui. Ça sent encore la pomme. Nino tient le verre à deux mains. Tu restes assis un moment ? Oui, maman. Bravo. Le soleil reste sur la table. Les pelures dorment dans le bol.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo entre dans la cuisine. Maman coupe des pommes. Ça sent le sucré. Hugo a soif. Sa bouche est sèche. Sa langue colle. Hugo dit : j'ai soif, maman. Maman sourit. Maman prend un verre. Le verre est bleu. Elle verse de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. L'eau est claire. Hugo prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Maman dit : quand on a soif, on boit de l'eau. Dans un verre. Hugo pose le verre. Il se sent mieux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les pelures de pomme s'enroulent. Elles font des rubans jaunes. Elles reposent sur la planche. Ça sent le sucré. Une abeille tapote la vitre. Tic. Tic. Nino habite ici, avec maman. Papa est au jardin, tout près. Le soleil entre sur la table. Tu as vu les rubans, Nino ? Ce sont des pelures, maman. Oui. Des rubans de pomme. On les pose dans le bol ? Oui, maman. Nino aide un peu. La planche est lisse. En ce moment, Nino a soif. Sa bouche est sèche. Sa langue colle. J'ai soif, maman. On prend un verre ? Oui. Maman prend un verre. Le verre est bleu. Elle verse de l'eau. L'eau est claire. Tu prends le verre d'eau ? Nino prend le verre. Il boit une gorgée. C'est frais. Il boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Nino pose le verre. Tu te sens mieux ? Oui, maman. Bravo, Nino. Tu as bu de l'eau. L'abeille tapote encore un peu. Tu l'entends, l'abeille ? Oui. Tic. Tic. Une goutte reste sur le verre bleu. Tu as vu la goutte ? Elle glisse, maman. Oui. Tout doux. Tu restes près de la table ? Oui. Ça sent encore la pomme. Nino tient le verre à deux mains. Tu restes assis un moment ? Oui, maman. Bravo. Le soleil reste sur la table. Les pelures dorment dans le bol.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,12 @@
 maman|Tu restes près de la table ?
 enfant-m|Oui.
 narrateur|Ça sent encore la pomme.
-narrateur|Nino tient le verre à deux mains.</t>
+narrateur|Nino tient le verre à deux mains.
+maman|Tu restes assis un moment ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Le soleil reste sur la table.
+narrateur|Les pelures dorment dans le bol.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1416,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo a &lt;emphasis level="moderate"&gt;soif&lt;/emphasis&gt;. Que prend-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a soif. Que prend-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1580,6 @@
 narrateur|Que prend-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. C'est du bon travail. Le verre est bleu, maman. Oui. Il est tout bleu. Tu veux encore une gorgée ? Oui. Nino boit encore un peu. Il pose le verre. Le verre reste sur la table ? Oui, maman.</t>
+          <t>Nino avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. Le verre est bleu, maman. Oui. Il est tout bleu. Tu veux encore une gorgée ? Oui. Nino boit encore un peu. Il pose le verre. Le verre reste sur la table ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo avait soif. Il a pris le verre. Il a bu de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino avait soif. Il a pris le verre. Il a bu de l'eau. Bravo. Le verre est bleu, maman. Oui. Il est tout bleu. Tu veux encore une gorgée ? Oui. Nino boit encore un peu. Il pose le verre. Le verre reste sur la table ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,7 +1752,6 @@
 narrateur|Il a pris le verre.
 narrateur|Il a bu de l'eau.
 maman|Bravo.
-maman|C'est du bon travail.
 enfant-m|Le verre est bleu, maman.
 maman|Oui. Il est tout bleu.
 maman|Tu veux encore une gorgée ?
@@ -1759,7 +1762,6 @@
 enfant-m|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1791,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo croque un morc&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt; de pomme. Le verre reste sur la table. Merci, dit Hugo.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu veux un morceau de pomme ? Oui, maman. Nino croque un morceau. Ça croque. C'est sucré. Oui. Sucré et croquant. Tu as fini de poser le verre ? Oui. Bravo. Le verre bleu reste sur la table. Les rubans jaunes restent dans le bol. L'abeille s'en va, hein ? Oui. Elle est partie. Merci, maman. Merci, Nino. On reste un moment à table ? Oui. Nino reste près de maman. Tu as fini ta petite pomme ? Oui, maman. Bravo. La planche est propre, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1948,7 +1950,6 @@
 narrateur|La planche est propre, maintenant.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1973,12 +1974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nino. Tu as fait du bon travail. Le verre bleu brille encore un peu. L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nino. Le verre bleu brille encore un peu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Nino. Le verre bleu brille encore un peu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2116,12 +2117,9 @@
           <t>enfant-m|J'avais soif.
 enfant-m|J'ai bu de l'eau.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
-narrateur|Le verre bleu brille encore un peu.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le verre bleu brille encore un peu.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2140,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2183,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-02.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
